--- a/balancete_receita.xlsx
+++ b/balancete_receita.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10F91E9B-705B-4238-8286-19C5DE9614CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{C54438B5-C092-42DC-9305-A37990FEFD22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105"/>
   </bookViews>
@@ -2120,6 +2120,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I425"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
